--- a/output/Test_Cases_collection/TC03 - Login with Invalid Password.xlsx
+++ b/output/Test_Cases_collection/TC03 - Login with Invalid Password.xlsx
@@ -37,7 +37,7 @@
     <t>Category</t>
   </si>
   <si>
-    <t>**TC03 - Login with Invalid Password**</t>
+    <t>TC03 - Login with Invalid Password</t>
   </si>
   <si>
     <t>0</t>
@@ -52,28 +52,28 @@
     <t>3</t>
   </si>
   <si>
-    <t>Launch the application and open `https://www.saucedemo.com/`.</t>
-  </si>
-  <si>
-    <t>Enter "standard_user" in the "user-name" field.</t>
-  </si>
-  <si>
-    <t>Enter "wrong_password" in the "password" field.</t>
-  </si>
-  <si>
-    <t>Click on "login-button".</t>
-  </si>
-  <si>
-    <t>The login page is displayed with username and password fields.</t>
-  </si>
-  <si>
-    <t>The username is entered successfully.</t>
-  </si>
-  <si>
-    <t>The password is entered successfully.</t>
-  </si>
-  <si>
-    <t>An error message is displayed: "Epic sadface: Username and password do not match any user in this service."</t>
+    <t>Launch the application and open `https://mindful-shark-fv3y29-dev-ed.trailblaze.lightning.force.com/`</t>
+  </si>
+  <si>
+    <t>Enter "rajaram111294@mindful-shark-fv3y29.com" in "Username" field</t>
+  </si>
+  <si>
+    <t>Enter "wrong_password" in "Password" field</t>
+  </si>
+  <si>
+    <t>Click on "Log In"</t>
+  </si>
+  <si>
+    <t>Salesforce Login Page is displayed with Username and Password fields.</t>
+  </si>
+  <si>
+    <t>Username is entered successfully.</t>
+  </si>
+  <si>
+    <t>Password is entered successfully.</t>
+  </si>
+  <si>
+    <t>Error message "Please check your username and password. If you still can't log in..." appears.</t>
   </si>
   <si>
     <t>New</t>
